--- a/Aviation/Resources/parts.xlsx
+++ b/Aviation/Resources/parts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="95">
   <si>
     <t>PartNumber</t>
   </si>
@@ -47,6 +47,255 @@
   </si>
   <si>
     <t>Aero Engine Corporation of China - Efficient turboprop for regional transport</t>
+  </si>
+  <si>
+    <t>5856D229</t>
+  </si>
+  <si>
+    <t>MTU Aero Engines - High-thrust afterburning turbojet</t>
+  </si>
+  <si>
+    <t>Turboprop</t>
+  </si>
+  <si>
+    <t>Honeywell - Lightweight engine for UAVs</t>
+  </si>
+  <si>
+    <t>A37F2FF4</t>
+  </si>
+  <si>
+    <t>IHI Corporation - Supersonic-capable ramjet engine</t>
+  </si>
+  <si>
+    <t>E71B3261</t>
+  </si>
+  <si>
+    <t>Rolls-Royce - Compact turbojet for military jets</t>
+  </si>
+  <si>
+    <t>Turboshaft</t>
+  </si>
+  <si>
+    <t>720DBEB5</t>
+  </si>
+  <si>
+    <t>Honeywell - Supersonic-capable ramjet engine</t>
+  </si>
+  <si>
+    <t>9FA194F0</t>
+  </si>
+  <si>
+    <t>Honeywell - Fuel-efficient engine for long-haul flights</t>
+  </si>
+  <si>
+    <t>Ramjet</t>
+  </si>
+  <si>
+    <t>E30D4DE1</t>
+  </si>
+  <si>
+    <t>Pratt &amp; Whitney - Compact turbojet for military jets</t>
+  </si>
+  <si>
+    <t>4992F7A3</t>
+  </si>
+  <si>
+    <t>Safran - Supersonic-capable ramjet engine</t>
+  </si>
+  <si>
+    <t>FDD70091</t>
+  </si>
+  <si>
+    <t>Klimov - Compact turbojet for military jets</t>
+  </si>
+  <si>
+    <t>D4359D18</t>
+  </si>
+  <si>
+    <t>1349B4F8</t>
+  </si>
+  <si>
+    <t>IHI Corporation - Efficient turboprop for regional transport</t>
+  </si>
+  <si>
+    <t>F2DB824B</t>
+  </si>
+  <si>
+    <t>Klimov - Quiet turbofan for business jets</t>
+  </si>
+  <si>
+    <t>EC05DD2B</t>
+  </si>
+  <si>
+    <t>Williams International - Efficient turboprop for regional transport</t>
+  </si>
+  <si>
+    <t>EC28FC2D</t>
+  </si>
+  <si>
+    <t>Honeywell - Helicopter engine with advanced cooling</t>
+  </si>
+  <si>
+    <t>CB81A8B9</t>
+  </si>
+  <si>
+    <t>Honeywell - Heavy-duty engine for cargo planes</t>
+  </si>
+  <si>
+    <t>42B1537A</t>
+  </si>
+  <si>
+    <t>Pratt &amp; Whitney - Helicopter engine with advanced cooling</t>
+  </si>
+  <si>
+    <t>A5A5674C</t>
+  </si>
+  <si>
+    <t>Aero Engine Corporation of China - High-bypass turbofan for commercial aircraft</t>
+  </si>
+  <si>
+    <t>43D20F6C</t>
+  </si>
+  <si>
+    <t>870A4F82</t>
+  </si>
+  <si>
+    <t>Rolls-Royce - Quiet turbofan for business jets</t>
+  </si>
+  <si>
+    <t>CB087A13</t>
+  </si>
+  <si>
+    <t>Pratt &amp; Whitney - Heavy-duty engine for cargo planes</t>
+  </si>
+  <si>
+    <t>111E4F2E</t>
+  </si>
+  <si>
+    <t>Aero Engine Corporation of China - Heavy-duty engine for cargo planes</t>
+  </si>
+  <si>
+    <t>ACA3A10C</t>
+  </si>
+  <si>
+    <t>GE Aviation - Fuel-efficient engine for long-haul flights</t>
+  </si>
+  <si>
+    <t>0C03B69F</t>
+  </si>
+  <si>
+    <t>4F955838</t>
+  </si>
+  <si>
+    <t>Williams International - High-bypass turbofan for commercial aircraft</t>
+  </si>
+  <si>
+    <t>Rolls-Royce - Fuel-efficient engine for long-haul flights</t>
+  </si>
+  <si>
+    <t>EC077881</t>
+  </si>
+  <si>
+    <t>IHI Corporation - Compact turbojet for military jets</t>
+  </si>
+  <si>
+    <t>B95A0A78</t>
+  </si>
+  <si>
+    <t>IHI Corporation - Helicopter engine with advanced cooling</t>
+  </si>
+  <si>
+    <t>5DCF2173</t>
+  </si>
+  <si>
+    <t>Klimov - Fuel-efficient engine for long-haul flights</t>
+  </si>
+  <si>
+    <t>E37AE1A3</t>
+  </si>
+  <si>
+    <t>Klimov - Lightweight engine for UAVs</t>
+  </si>
+  <si>
+    <t>221F6F3C</t>
+  </si>
+  <si>
+    <t>Klimov - Helicopter engine with advanced cooling</t>
+  </si>
+  <si>
+    <t>92F07822</t>
+  </si>
+  <si>
+    <t>4D9343D5</t>
+  </si>
+  <si>
+    <t>Safran - High-bypass turbofan for commercial aircraft</t>
+  </si>
+  <si>
+    <t>AA528FEA</t>
+  </si>
+  <si>
+    <t>Safran - Heavy-duty engine for cargo planes</t>
+  </si>
+  <si>
+    <t>698DB3CA</t>
+  </si>
+  <si>
+    <t>Rolls-Royce - Lightweight engine for UAVs</t>
+  </si>
+  <si>
+    <t>Safran - Compact turbojet for military jets</t>
+  </si>
+  <si>
+    <t>DE413017</t>
+  </si>
+  <si>
+    <t>7F33F88E</t>
+  </si>
+  <si>
+    <t>1E936256</t>
+  </si>
+  <si>
+    <t>MTU Aero Engines - Compact turbojet for military jets</t>
+  </si>
+  <si>
+    <t>D412D47C</t>
+  </si>
+  <si>
+    <t>E479D343</t>
+  </si>
+  <si>
+    <t>B6B479E0</t>
+  </si>
+  <si>
+    <t>1F50637D</t>
+  </si>
+  <si>
+    <t>Pratt &amp; Whitney - Fuel-efficient engine for long-haul flights</t>
+  </si>
+  <si>
+    <t>3148F961</t>
+  </si>
+  <si>
+    <t>626C7596</t>
+  </si>
+  <si>
+    <t>2566DFC3</t>
+  </si>
+  <si>
+    <t>Rolls-Royce - Heavy-duty engine for cargo planes</t>
+  </si>
+  <si>
+    <t>7FCAF514</t>
+  </si>
+  <si>
+    <t>Aero Engine Corporation of China - Compact turbojet for military jets</t>
+  </si>
+  <si>
+    <t>FCB854B1</t>
+  </si>
+  <si>
+    <t>Safran - Helicopter engine with advanced cooling</t>
   </si>
 </sst>
 </file>
@@ -80,11 +329,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -360,6 +612,664 @@
         <v>6</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1367068.59</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>8.4050005E7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3321514.18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2574099.88</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4940496.96</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>831737.22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2744518.15</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1679635.39</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1606412.5</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1">
+        <v>732855.88</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4701154.04</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="1">
+        <v>939624.14</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1384733.29</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2822207.71</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="1">
+        <v>3234441.96</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2146191.44</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1860275.02</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2351920.95</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3785803.18</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1474074.46</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3060962.99</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3807983.48</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="1">
+        <v>516438.39</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2069837.06</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3362119.16</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>2.705E277</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1463439.9</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2530217.42</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2122863.23</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1097497.41</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="1">
+        <v>4667427.13</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="1">
+        <v>795242.36</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="1">
+        <v>3143195.11</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="1">
+        <v>674812.67</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2501878.53</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3695323.51</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1">
+        <v>4.429111E7</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="1">
+        <v>890530.47</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3381217.96</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="1">
+        <v>4759159.9</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1508050.12</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="1">
+        <v>3052326.96</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="1">
+        <v>4882282.99</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2450427.45</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" s="1">
+        <v>808603.24</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="1">
+        <v>3258122.1</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="1">
+        <v>3755059.89</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2113343.6</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50" s="1">
+        <v>3880856.38</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51" s="1">
+        <v>1975349.64</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Aviation/Resources/parts.xlsx
+++ b/Aviation/Resources/parts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="97">
   <si>
     <t>PartNumber</t>
   </si>
@@ -23,6 +23,12 @@
   </si>
   <si>
     <t>EngineType</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Threshold</t>
   </si>
   <si>
     <t>0579AECB</t>
@@ -569,61 +575,91 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1">
         <v>3212436.93</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E2" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>3654294.49</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E3" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1">
         <v>4876983.64</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E4" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
         <v>1367068.59</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E5" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="6">
@@ -631,321 +667,459 @@
         <v>8.4050005E7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1">
         <v>3321514.18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E6" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1">
         <v>2574099.88</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1">
         <v>4940496.96</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E8" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1">
         <v>831737.22</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E9" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1">
         <v>2744518.15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E10" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1">
         <v>1679635.39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E11" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1">
         <v>1606412.5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E12" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1">
         <v>732855.88</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E13" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1">
         <v>4701154.04</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E14" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1">
         <v>939624.14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E15" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1">
         <v>1384733.29</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E16" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1">
         <v>2822207.71</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E17" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1">
         <v>3234441.96</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E18" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1">
         <v>2146191.44</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E19" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1">
         <v>1860275.02</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E20" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1">
         <v>2351920.95</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E21" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C22" s="1">
         <v>3785803.18</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E22" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23" s="1">
         <v>1474074.46</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E23" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C24" s="1">
         <v>3060962.99</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E24" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C25" s="1">
         <v>3807983.48</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E25" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C26" s="1">
         <v>516438.39</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E26" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C27" s="1">
         <v>2069837.06</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E27" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C28" s="1">
         <v>3362119.16</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E28" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="29">
@@ -953,139 +1127,199 @@
         <v>2.705E277</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C29" s="1">
         <v>1463439.9</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E29" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="F29" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C30" s="1">
         <v>2530217.42</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E30" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F30" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C31" s="1">
         <v>2122863.23</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E31" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F31" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C32" s="1">
         <v>1097497.41</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E32" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="F32" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C33" s="1">
         <v>4667427.13</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E33" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F33" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C34" s="1">
         <v>795242.36</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E34" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F34" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C35" s="1">
         <v>3143195.11</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E35" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F35" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C36" s="1">
         <v>674812.67</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E36" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F36" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C37" s="1">
         <v>2501878.53</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E37" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F37" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C38" s="1">
         <v>3695323.51</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E38" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F38" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="39">
@@ -1093,181 +1327,259 @@
         <v>4.429111E7</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C39" s="1">
         <v>890530.47</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E39" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="C40" s="1">
         <v>3381217.96</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E40" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C41" s="1">
         <v>4759159.9</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E41" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C42" s="1">
         <v>1508050.12</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E42" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F42" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C43" s="1">
         <v>3052326.96</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E43" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="F43" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C44" s="1">
         <v>4882282.99</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E44" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F44" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C45" s="1">
         <v>2450427.45</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E45" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F45" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C46" s="1">
         <v>808603.24</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E46" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="F46" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C47" s="1">
         <v>3258122.1</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E47" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F47" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C48" s="1">
         <v>3755059.89</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E48" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="F48" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C49" s="1">
         <v>2113343.6</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E49" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="F49" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C50" s="1">
         <v>3880856.38</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E50" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F50" s="1">
+        <v>5.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C51" s="1">
         <v>1975349.64</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E51" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F51" s="1">
+        <v>5.0</v>
       </c>
     </row>
   </sheetData>

--- a/Aviation/Resources/parts.xlsx
+++ b/Aviation/Resources/parts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="95">
   <si>
     <t>PartNumber</t>
   </si>
@@ -23,12 +23,6 @@
   </si>
   <si>
     <t>EngineType</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Threshold</t>
   </si>
   <si>
     <t>0579AECB</t>
@@ -575,91 +569,61 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1">
         <v>3212436.93</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="F2" s="1">
-        <v>5.0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>3654294.49</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F3" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>4876983.64</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F4" s="1">
-        <v>5.0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1">
         <v>1367068.59</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>5.0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -667,459 +631,321 @@
         <v>8.4050005E7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
         <v>3321514.18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>5.0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1">
         <v>2574099.88</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
         <v>4940496.96</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>5.0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1">
         <v>831737.22</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F9" s="1">
-        <v>5.0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1">
         <v>2744518.15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F10" s="1">
-        <v>5.0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1">
         <v>1679635.39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F11" s="1">
-        <v>5.0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1">
         <v>1606412.5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F12" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1">
         <v>732855.88</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F13" s="1">
-        <v>5.0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1">
         <v>4701154.04</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F14" s="1">
-        <v>5.0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" s="1">
         <v>939624.14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F15" s="1">
-        <v>5.0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C16" s="1">
         <v>1384733.29</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F16" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C17" s="1">
         <v>2822207.71</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F17" s="1">
-        <v>5.0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1">
         <v>3234441.96</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F18" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C19" s="1">
         <v>2146191.44</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="F19" s="1">
-        <v>5.0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1">
         <v>1860275.02</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="F20" s="1">
-        <v>5.0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C21" s="1">
         <v>2351920.95</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F21" s="1">
-        <v>5.0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C22" s="1">
         <v>3785803.18</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="F22" s="1">
-        <v>5.0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C23" s="1">
         <v>1474074.46</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F23" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C24" s="1">
         <v>3060962.99</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="F24" s="1">
-        <v>5.0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C25" s="1">
         <v>3807983.48</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F25" s="1">
-        <v>5.0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C26" s="1">
         <v>516438.39</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="F26" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C27" s="1">
         <v>2069837.06</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F27" s="1">
-        <v>5.0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C28" s="1">
         <v>3362119.16</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F28" s="1">
-        <v>5.0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1127,199 +953,139 @@
         <v>2.705E277</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C29" s="1">
         <v>1463439.9</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="F29" s="1">
-        <v>5.0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C30" s="1">
         <v>2530217.42</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F30" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1">
         <v>2122863.23</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F31" s="1">
-        <v>5.0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C32" s="1">
         <v>1097497.41</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>5.0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C33" s="1">
         <v>4667427.13</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F33" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C34" s="1">
         <v>795242.36</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F34" s="1">
-        <v>5.0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C35" s="1">
         <v>3143195.11</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F35" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C36" s="1">
         <v>674812.67</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F36" s="1">
-        <v>5.0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1">
         <v>2501878.53</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F37" s="1">
-        <v>5.0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C38" s="1">
         <v>3695323.51</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F38" s="1">
-        <v>5.0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
@@ -1327,259 +1093,181 @@
         <v>4.429111E7</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C39" s="1">
         <v>890530.47</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E39" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F39" s="1">
-        <v>5.0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C40" s="1">
         <v>3381217.96</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E40" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="F40" s="1">
-        <v>5.0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C41" s="1">
         <v>4759159.9</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F41" s="1">
-        <v>5.0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C42" s="1">
         <v>1508050.12</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F42" s="1">
-        <v>5.0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C43" s="1">
         <v>3052326.96</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="F43" s="1">
-        <v>5.0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C44" s="1">
         <v>4882282.99</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F44" s="1">
-        <v>5.0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C45" s="1">
         <v>2450427.45</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F45" s="1">
-        <v>5.0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C46" s="1">
         <v>808603.24</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="F46" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C47" s="1">
         <v>3258122.1</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F47" s="1">
-        <v>5.0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C48" s="1">
         <v>3755059.89</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="F48" s="1">
-        <v>5.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C49" s="1">
         <v>2113343.6</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E49" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="F49" s="1">
-        <v>5.0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C50" s="1">
         <v>3880856.38</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F50" s="1">
-        <v>5.0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C51" s="1">
         <v>1975349.64</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F51" s="1">
-        <v>5.0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
